--- a/samples/O_科目余额表.xlsx
+++ b/samples/O_科目余额表.xlsx
@@ -438,11 +438,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -535,21 +535,111 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5100000</v>
+        <v>5800000</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>28000000</v>
+        <v>12000000</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>27500000</v>
+        <v>11500000</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5600000</v>
+        <v>6300000</v>
       </c>
       <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>委托加工物资</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>800000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>750000</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>550000</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>存货跌价准备</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>生产成本</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>800000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/samples/O_科目余额表.xlsx
+++ b/samples/O_科目余额表.xlsx
@@ -442,7 +442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
